--- a/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92540050559</v>
+        <v>46157.93114176577</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114176577</v>
+        <v>46157.93368272818</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93368272818</v>
+        <v>46157.93672071151</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93672071151</v>
+        <v>46158.28194181993</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28194181993</v>
+        <v>46158.29718322066</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29718322066</v>
+        <v>46158.29790388078</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29790388078</v>
+        <v>46158.33355925148</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33355925148</v>
+        <v>46158.37210757397</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37210757397</v>
+        <v>46158.37267753074</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
